--- a/Newdata/鑄件未交.XLSX
+++ b/Newdata/鑄件未交.XLSX
@@ -29980,7 +29980,7 @@
         <v>1</v>
       </c>
       <c r="D473" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E473" t="s">
         <v>1165</v>
@@ -29998,7 +29998,7 @@
         <v>45875</v>
       </c>
       <c r="J473" t="s">
-        <v>17</v>
+        <v>984</v>
       </c>
       <c r="K473" t="s">
         <v>57</v>
@@ -45028,7 +45028,7 @@
         <v>40</v>
       </c>
       <c r="D774" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E774" t="s">
         <v>1760</v>
@@ -45046,7 +45046,7 @@
         <v>46153</v>
       </c>
       <c r="J774" t="s">
-        <v>17</v>
+        <v>984</v>
       </c>
       <c r="K774" t="s">
         <v>5</v>
@@ -49428,7 +49428,7 @@
         <v>1</v>
       </c>
       <c r="D862" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E862" t="s">
         <v>1918</v>
@@ -49446,7 +49446,7 @@
         <v>46189</v>
       </c>
       <c r="J862" t="s">
-        <v>1235</v>
+        <v>1711</v>
       </c>
       <c r="K862" t="s">
         <v>57</v>

--- a/Newdata/鑄件未交.XLSX
+++ b/Newdata/鑄件未交.XLSX
@@ -35416,7 +35416,7 @@
         <v>3</v>
       </c>
       <c r="D582" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E582" t="s">
         <v>905</v>
@@ -35434,7 +35434,7 @@
         <v>46083</v>
       </c>
       <c r="J582" t="s">
-        <v>36</v>
+        <v>984</v>
       </c>
       <c r="K582" t="s">
         <v>57</v>
@@ -50766,7 +50766,7 @@
         <v>1</v>
       </c>
       <c r="D889" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E889" t="s">
         <v>868</v>
@@ -50784,7 +50784,7 @@
         <v>46219</v>
       </c>
       <c r="J889" t="s">
-        <v>1232</v>
+        <v>1708</v>
       </c>
       <c r="K889" t="s">
         <v>57</v>
@@ -52116,7 +52116,7 @@
         <v>1</v>
       </c>
       <c r="D916" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E916" t="s">
         <v>865</v>
@@ -52134,7 +52134,7 @@
         <v>46223</v>
       </c>
       <c r="J916" t="s">
-        <v>1232</v>
+        <v>1708</v>
       </c>
       <c r="K916" t="s">
         <v>57</v>

--- a/Newdata/鑄件未交.XLSX
+++ b/Newdata/鑄件未交.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9316" uniqueCount="2059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9326" uniqueCount="2063">
   <si>
     <t>ZP04</t>
   </si>
@@ -5234,6 +5234,9 @@
     <t>8814001354B0</t>
   </si>
   <si>
+    <t>REL  PRC  MANC NMAT RMWB SETC</t>
+  </si>
+  <si>
     <t>400006376</t>
   </si>
   <si>
@@ -5988,6 +5991,9 @@
     <t>400006532</t>
   </si>
   <si>
+    <t>PREL PRC  MANC NMAT RMWB SETC</t>
+  </si>
+  <si>
     <t>400006533</t>
   </si>
   <si>
@@ -6066,6 +6072,24 @@
     <t>工作台加工圖_6000L*2200W*260H,HSA-623/627</t>
   </si>
   <si>
+    <t>400006554</t>
+  </si>
+  <si>
+    <t>8810001553A0</t>
+  </si>
+  <si>
+    <t>底座加工圖,三線軌_LG-1370 NEO</t>
+  </si>
+  <si>
+    <t>400006555</t>
+  </si>
+  <si>
+    <t>8814001379B1</t>
+  </si>
+  <si>
+    <t>機頭加工圖,G8K,Z1000_HSA-x23,四線軌用</t>
+  </si>
+  <si>
     <t>ZP09</t>
   </si>
   <si>
@@ -6109,18 +6133,6 @@
   </si>
   <si>
     <t>REL  PRC  MANC RMWB SETC</t>
-  </si>
-  <si>
-    <t>630000351</t>
-  </si>
-  <si>
-    <t>080100076704</t>
-  </si>
-  <si>
-    <t>P12K 主軸,021444_BT40,8YU,CWDIN</t>
-  </si>
-  <si>
-    <t>REL  PCNF DLV  PRC  MANC RMWB SETC</t>
   </si>
   <si>
     <t>630000354</t>
@@ -6294,7 +6306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P931"/>
+  <dimension ref="A1:P932"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -6317,52 +6329,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2045</v>
+        <v>2049</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2046</v>
+        <v>2050</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2048</v>
+        <v>2052</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2049</v>
+        <v>2053</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2050</v>
+        <v>2054</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2052</v>
+        <v>2056</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2055</v>
+        <v>2059</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -38386,7 +38398,7 @@
         <v>46146</v>
       </c>
       <c r="J642" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="K642" t="s">
         <v>54</v>
@@ -43486,7 +43498,7 @@
         <v>46167</v>
       </c>
       <c r="J744" t="s">
-        <v>201</v>
+        <v>17</v>
       </c>
       <c r="K744" t="s">
         <v>54</v>
@@ -44236,7 +44248,7 @@
         <v>46265</v>
       </c>
       <c r="J759" t="s">
-        <v>21</v>
+        <v>1740</v>
       </c>
       <c r="K759" t="s">
         <v>5</v>
@@ -44262,7 +44274,7 @@
         <v>0</v>
       </c>
       <c r="B760" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="C760" s="2">
         <v>12</v>
@@ -44312,7 +44324,7 @@
         <v>0</v>
       </c>
       <c r="B761" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="C761" s="2">
         <v>12</v>
@@ -44362,7 +44374,7 @@
         <v>0</v>
       </c>
       <c r="B762" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="C762" s="2">
         <v>12</v>
@@ -44412,7 +44424,7 @@
         <v>0</v>
       </c>
       <c r="B763" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="C763" s="2">
         <v>80</v>
@@ -44462,7 +44474,7 @@
         <v>0</v>
       </c>
       <c r="B764" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="C764" s="2">
         <v>60</v>
@@ -44512,7 +44524,7 @@
         <v>0</v>
       </c>
       <c r="B765" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="C765" s="2">
         <v>40</v>
@@ -44521,10 +44533,10 @@
         <v>0</v>
       </c>
       <c r="E765" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="F765" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="G765" s="3">
         <v>46092</v>
@@ -44562,7 +44574,7 @@
         <v>0</v>
       </c>
       <c r="B766" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="C766" s="2">
         <v>12</v>
@@ -44612,7 +44624,7 @@
         <v>0</v>
       </c>
       <c r="B767" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="C767" s="2">
         <v>2</v>
@@ -44621,10 +44633,10 @@
         <v>0</v>
       </c>
       <c r="E767" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="F767" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G767" s="3">
         <v>46092</v>
@@ -44662,7 +44674,7 @@
         <v>0</v>
       </c>
       <c r="B768" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="C768" s="2">
         <v>4</v>
@@ -44671,10 +44683,10 @@
         <v>0</v>
       </c>
       <c r="E768" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="F768" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G768" s="3">
         <v>46092</v>
@@ -44712,7 +44724,7 @@
         <v>0</v>
       </c>
       <c r="B769" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="C769" s="2">
         <v>2</v>
@@ -44762,7 +44774,7 @@
         <v>0</v>
       </c>
       <c r="B770" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="C770" s="2">
         <v>1</v>
@@ -44771,10 +44783,10 @@
         <v>0</v>
       </c>
       <c r="E770" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="F770" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G770" s="3">
         <v>46092</v>
@@ -44812,7 +44824,7 @@
         <v>0</v>
       </c>
       <c r="B771" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="C771" s="2">
         <v>1</v>
@@ -44821,10 +44833,10 @@
         <v>0</v>
       </c>
       <c r="E771" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="F771" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G771" s="3">
         <v>46092</v>
@@ -44862,7 +44874,7 @@
         <v>0</v>
       </c>
       <c r="B772" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="C772" s="2">
         <v>3</v>
@@ -44912,7 +44924,7 @@
         <v>0</v>
       </c>
       <c r="B773" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="C773" s="2">
         <v>20</v>
@@ -44921,10 +44933,10 @@
         <v>0</v>
       </c>
       <c r="E773" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="F773" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="G773" s="3">
         <v>46094</v>
@@ -44962,7 +44974,7 @@
         <v>0</v>
       </c>
       <c r="B774" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C774" s="2">
         <v>20</v>
@@ -44971,10 +44983,10 @@
         <v>0</v>
       </c>
       <c r="E774" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="F774" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G774" s="3">
         <v>46094</v>
@@ -45012,7 +45024,7 @@
         <v>0</v>
       </c>
       <c r="B775" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C775" s="2">
         <v>20</v>
@@ -45062,7 +45074,7 @@
         <v>0</v>
       </c>
       <c r="B776" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="C776" s="2">
         <v>3</v>
@@ -45112,7 +45124,7 @@
         <v>0</v>
       </c>
       <c r="B777" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C777" s="2">
         <v>80</v>
@@ -45162,7 +45174,7 @@
         <v>0</v>
       </c>
       <c r="B778" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="C778" s="2">
         <v>3</v>
@@ -45212,7 +45224,7 @@
         <v>0</v>
       </c>
       <c r="B779" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C779" s="2">
         <v>1</v>
@@ -45221,10 +45233,10 @@
         <v>0</v>
       </c>
       <c r="E779" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="F779" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="G779" s="3">
         <v>46094</v>
@@ -45262,7 +45274,7 @@
         <v>0</v>
       </c>
       <c r="B780" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="C780" s="2">
         <v>10</v>
@@ -45312,7 +45324,7 @@
         <v>0</v>
       </c>
       <c r="B781" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C781" s="2">
         <v>5</v>
@@ -45362,7 +45374,7 @@
         <v>0</v>
       </c>
       <c r="B782" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="C782" s="2">
         <v>10</v>
@@ -45371,7 +45383,7 @@
         <v>0</v>
       </c>
       <c r="E782" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="F782" t="s">
         <v>759</v>
@@ -45412,7 +45424,7 @@
         <v>0</v>
       </c>
       <c r="B783" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="C783" s="2">
         <v>5</v>
@@ -45421,7 +45433,7 @@
         <v>0</v>
       </c>
       <c r="E783" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="F783" t="s">
         <v>366</v>
@@ -45462,7 +45474,7 @@
         <v>0</v>
       </c>
       <c r="B784" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C784" s="2">
         <v>40</v>
@@ -45512,7 +45524,7 @@
         <v>0</v>
       </c>
       <c r="B785" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C785" s="2">
         <v>20</v>
@@ -45521,10 +45533,10 @@
         <v>0</v>
       </c>
       <c r="E785" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="F785" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G785" s="3">
         <v>46098</v>
@@ -45562,7 +45574,7 @@
         <v>0</v>
       </c>
       <c r="B786" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="C786" s="2">
         <v>20</v>
@@ -45571,10 +45583,10 @@
         <v>0</v>
       </c>
       <c r="E786" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="F786" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="G786" s="3">
         <v>46098</v>
@@ -45612,7 +45624,7 @@
         <v>0</v>
       </c>
       <c r="B787" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C787" s="2">
         <v>20</v>
@@ -45621,10 +45633,10 @@
         <v>0</v>
       </c>
       <c r="E787" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="F787" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G787" s="3">
         <v>46098</v>
@@ -45662,7 +45674,7 @@
         <v>0</v>
       </c>
       <c r="B788" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="C788" s="2">
         <v>20</v>
@@ -45671,10 +45683,10 @@
         <v>0</v>
       </c>
       <c r="E788" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="F788" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="G788" s="3">
         <v>46098</v>
@@ -45712,7 +45724,7 @@
         <v>0</v>
       </c>
       <c r="B789" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C789" s="2">
         <v>1</v>
@@ -45762,7 +45774,7 @@
         <v>0</v>
       </c>
       <c r="B790" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="C790" s="2">
         <v>2</v>
@@ -45812,7 +45824,7 @@
         <v>0</v>
       </c>
       <c r="B791" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C791" s="2">
         <v>2</v>
@@ -45821,10 +45833,10 @@
         <v>1</v>
       </c>
       <c r="E791" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="F791" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="G791" s="3">
         <v>46098</v>
@@ -45862,7 +45874,7 @@
         <v>0</v>
       </c>
       <c r="B792" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="C792" s="2">
         <v>2</v>
@@ -45871,10 +45883,10 @@
         <v>1</v>
       </c>
       <c r="E792" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="F792" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="G792" s="3">
         <v>46098</v>
@@ -45912,7 +45924,7 @@
         <v>0</v>
       </c>
       <c r="B793" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C793" s="2">
         <v>6</v>
@@ -45962,7 +45974,7 @@
         <v>0</v>
       </c>
       <c r="B794" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="C794" s="2">
         <v>6</v>
@@ -46012,7 +46024,7 @@
         <v>0</v>
       </c>
       <c r="B795" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C795" s="2">
         <v>3</v>
@@ -46062,7 +46074,7 @@
         <v>0</v>
       </c>
       <c r="B796" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C796" s="2">
         <v>3</v>
@@ -46112,7 +46124,7 @@
         <v>0</v>
       </c>
       <c r="B797" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C797" s="2">
         <v>40</v>
@@ -46121,10 +46133,10 @@
         <v>0</v>
       </c>
       <c r="E797" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="F797" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="G797" s="3">
         <v>46098</v>
@@ -46162,7 +46174,7 @@
         <v>0</v>
       </c>
       <c r="B798" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="C798" s="2">
         <v>6</v>
@@ -46212,7 +46224,7 @@
         <v>0</v>
       </c>
       <c r="B799" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="C799" s="2">
         <v>2</v>
@@ -46262,7 +46274,7 @@
         <v>0</v>
       </c>
       <c r="B800" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="C800" s="2">
         <v>2</v>
@@ -46271,10 +46283,10 @@
         <v>0</v>
       </c>
       <c r="E800" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="F800" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G800" s="3">
         <v>46099</v>
@@ -46312,7 +46324,7 @@
         <v>0</v>
       </c>
       <c r="B801" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C801" s="2">
         <v>1</v>
@@ -46362,7 +46374,7 @@
         <v>0</v>
       </c>
       <c r="B802" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="C802" s="2">
         <v>8</v>
@@ -46412,7 +46424,7 @@
         <v>0</v>
       </c>
       <c r="B803" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="C803" s="2">
         <v>12</v>
@@ -46421,10 +46433,10 @@
         <v>12</v>
       </c>
       <c r="E803" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="F803" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="G803" s="3">
         <v>46104</v>
@@ -46462,7 +46474,7 @@
         <v>0</v>
       </c>
       <c r="B804" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C804" s="2">
         <v>12</v>
@@ -46471,10 +46483,10 @@
         <v>12</v>
       </c>
       <c r="E804" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="F804" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="G804" s="3">
         <v>46104</v>
@@ -46512,7 +46524,7 @@
         <v>0</v>
       </c>
       <c r="B805" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="C805" s="2">
         <v>3</v>
@@ -46562,7 +46574,7 @@
         <v>0</v>
       </c>
       <c r="B806" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="C806" s="2">
         <v>1</v>
@@ -46571,10 +46583,10 @@
         <v>0</v>
       </c>
       <c r="E806" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="F806" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="G806" s="3">
         <v>46104</v>
@@ -46612,7 +46624,7 @@
         <v>0</v>
       </c>
       <c r="B807" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C807" s="2">
         <v>1</v>
@@ -46621,10 +46633,10 @@
         <v>0</v>
       </c>
       <c r="E807" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="F807" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="G807" s="3">
         <v>46104</v>
@@ -46662,7 +46674,7 @@
         <v>0</v>
       </c>
       <c r="B808" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C808" s="2">
         <v>5</v>
@@ -46712,7 +46724,7 @@
         <v>0</v>
       </c>
       <c r="B809" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C809" s="2">
         <v>20</v>
@@ -46721,10 +46733,10 @@
         <v>0</v>
       </c>
       <c r="E809" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="F809" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="G809" s="3">
         <v>46105</v>
@@ -46762,7 +46774,7 @@
         <v>0</v>
       </c>
       <c r="B810" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="C810" s="2">
         <v>1</v>
@@ -46771,10 +46783,10 @@
         <v>0</v>
       </c>
       <c r="E810" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="F810" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="G810" s="3">
         <v>46105</v>
@@ -46812,7 +46824,7 @@
         <v>0</v>
       </c>
       <c r="B811" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="C811" s="2">
         <v>1</v>
@@ -46821,10 +46833,10 @@
         <v>0</v>
       </c>
       <c r="E811" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="F811" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G811" s="3">
         <v>46105</v>
@@ -46862,7 +46874,7 @@
         <v>0</v>
       </c>
       <c r="B812" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C812" s="2">
         <v>2</v>
@@ -46912,7 +46924,7 @@
         <v>0</v>
       </c>
       <c r="B813" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="C813" s="2">
         <v>30</v>
@@ -46962,7 +46974,7 @@
         <v>0</v>
       </c>
       <c r="B814" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C814" s="2">
         <v>2</v>
@@ -47012,7 +47024,7 @@
         <v>0</v>
       </c>
       <c r="B815" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="C815" s="2">
         <v>3</v>
@@ -47062,7 +47074,7 @@
         <v>0</v>
       </c>
       <c r="B816" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C816" s="2">
         <v>4</v>
@@ -47112,7 +47124,7 @@
         <v>0</v>
       </c>
       <c r="B817" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="C817" s="2">
         <v>1</v>
@@ -47121,10 +47133,10 @@
         <v>1</v>
       </c>
       <c r="E817" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="F817" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="G817" s="3">
         <v>46107</v>
@@ -47162,7 +47174,7 @@
         <v>0</v>
       </c>
       <c r="B818" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C818" s="2">
         <v>60</v>
@@ -47212,7 +47224,7 @@
         <v>0</v>
       </c>
       <c r="B819" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="C819" s="2">
         <v>1</v>
@@ -47262,7 +47274,7 @@
         <v>0</v>
       </c>
       <c r="B820" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="C820" s="2">
         <v>5</v>
@@ -47286,7 +47298,7 @@
         <v>46205</v>
       </c>
       <c r="J820" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K820" t="s">
         <v>54</v>
@@ -47312,7 +47324,7 @@
         <v>0</v>
       </c>
       <c r="B821" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="C821" s="2">
         <v>5</v>
@@ -47362,7 +47374,7 @@
         <v>0</v>
       </c>
       <c r="B822" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="C822" s="2">
         <v>5</v>
@@ -47386,7 +47398,7 @@
         <v>46195</v>
       </c>
       <c r="J822" t="s">
-        <v>1849</v>
+        <v>1213</v>
       </c>
       <c r="K822" t="s">
         <v>54</v>
@@ -47412,7 +47424,7 @@
         <v>0</v>
       </c>
       <c r="B823" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C823" s="2">
         <v>5</v>
@@ -47436,7 +47448,7 @@
         <v>46195</v>
       </c>
       <c r="J823" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K823" t="s">
         <v>54</v>
@@ -47462,7 +47474,7 @@
         <v>0</v>
       </c>
       <c r="B824" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="C824" s="2">
         <v>1</v>
@@ -47512,7 +47524,7 @@
         <v>0</v>
       </c>
       <c r="B825" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C825" s="2">
         <v>3</v>
@@ -47562,7 +47574,7 @@
         <v>0</v>
       </c>
       <c r="B826" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="C826" s="2">
         <v>3</v>
@@ -47612,7 +47624,7 @@
         <v>0</v>
       </c>
       <c r="B827" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C827" s="2">
         <v>3</v>
@@ -47636,7 +47648,7 @@
         <v>46198</v>
       </c>
       <c r="J827" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K827" t="s">
         <v>54</v>
@@ -47662,7 +47674,7 @@
         <v>0</v>
       </c>
       <c r="B828" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="C828" s="2">
         <v>3</v>
@@ -47686,7 +47698,7 @@
         <v>46198</v>
       </c>
       <c r="J828" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K828" t="s">
         <v>54</v>
@@ -47712,7 +47724,7 @@
         <v>0</v>
       </c>
       <c r="B829" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C829" s="2">
         <v>2</v>
@@ -47762,7 +47774,7 @@
         <v>0</v>
       </c>
       <c r="B830" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="C830" s="2">
         <v>2</v>
@@ -47812,7 +47824,7 @@
         <v>0</v>
       </c>
       <c r="B831" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="C831" s="2">
         <v>3</v>
@@ -47821,10 +47833,10 @@
         <v>2</v>
       </c>
       <c r="E831" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="F831" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="G831" s="3">
         <v>46112</v>
@@ -47836,7 +47848,7 @@
         <v>46153</v>
       </c>
       <c r="J831" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="K831" t="s">
         <v>5</v>
@@ -47862,7 +47874,7 @@
         <v>0</v>
       </c>
       <c r="B832" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="C832" s="2">
         <v>2</v>
@@ -47871,10 +47883,10 @@
         <v>0</v>
       </c>
       <c r="E832" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="F832" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G832" s="3">
         <v>46113</v>
@@ -47912,7 +47924,7 @@
         <v>0</v>
       </c>
       <c r="B833" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C833" s="2">
         <v>10</v>
@@ -47962,7 +47974,7 @@
         <v>0</v>
       </c>
       <c r="B834" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="C834" s="2">
         <v>2</v>
@@ -47971,10 +47983,10 @@
         <v>0</v>
       </c>
       <c r="E834" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="F834" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="G834" s="3">
         <v>46114</v>
@@ -48012,7 +48024,7 @@
         <v>0</v>
       </c>
       <c r="B835" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C835" s="2">
         <v>1</v>
@@ -48021,10 +48033,10 @@
         <v>0</v>
       </c>
       <c r="E835" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="F835" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="G835" s="3">
         <v>46114</v>
@@ -48036,7 +48048,7 @@
         <v>46202</v>
       </c>
       <c r="J835" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K835" t="s">
         <v>54</v>
@@ -48062,7 +48074,7 @@
         <v>0</v>
       </c>
       <c r="B836" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="C836" s="2">
         <v>1</v>
@@ -48071,10 +48083,10 @@
         <v>0</v>
       </c>
       <c r="E836" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="F836" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="G836" s="3">
         <v>46114</v>
@@ -48086,7 +48098,7 @@
         <v>46202</v>
       </c>
       <c r="J836" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K836" t="s">
         <v>54</v>
@@ -48112,7 +48124,7 @@
         <v>0</v>
       </c>
       <c r="B837" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C837" s="2">
         <v>1</v>
@@ -48121,10 +48133,10 @@
         <v>0</v>
       </c>
       <c r="E837" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="F837" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="G837" s="3">
         <v>46114</v>
@@ -48162,7 +48174,7 @@
         <v>0</v>
       </c>
       <c r="B838" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="C838" s="2">
         <v>2</v>
@@ -48212,7 +48224,7 @@
         <v>0</v>
       </c>
       <c r="B839" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="C839" s="2">
         <v>1</v>
@@ -48221,10 +48233,10 @@
         <v>0</v>
       </c>
       <c r="E839" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="F839" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="G839" s="3">
         <v>46114</v>
@@ -48236,7 +48248,7 @@
         <v>46202</v>
       </c>
       <c r="J839" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K839" t="s">
         <v>54</v>
@@ -48262,7 +48274,7 @@
         <v>0</v>
       </c>
       <c r="B840" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C840" s="2">
         <v>1</v>
@@ -48271,10 +48283,10 @@
         <v>0</v>
       </c>
       <c r="E840" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="F840" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="G840" s="3">
         <v>46114</v>
@@ -48286,7 +48298,7 @@
         <v>46202</v>
       </c>
       <c r="J840" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K840" t="s">
         <v>54</v>
@@ -48312,7 +48324,7 @@
         <v>0</v>
       </c>
       <c r="B841" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C841" s="2">
         <v>2</v>
@@ -48336,7 +48348,7 @@
         <v>46217</v>
       </c>
       <c r="J841" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K841" t="s">
         <v>54</v>
@@ -48362,7 +48374,7 @@
         <v>0</v>
       </c>
       <c r="B842" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C842" s="2">
         <v>32</v>
@@ -48412,7 +48424,7 @@
         <v>0</v>
       </c>
       <c r="B843" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C843" s="2">
         <v>5</v>
@@ -48462,7 +48474,7 @@
         <v>0</v>
       </c>
       <c r="B844" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="C844" s="2">
         <v>5</v>
@@ -48512,7 +48524,7 @@
         <v>0</v>
       </c>
       <c r="B845" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="C845" s="2">
         <v>1</v>
@@ -48521,10 +48533,10 @@
         <v>0</v>
       </c>
       <c r="E845" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="F845" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G845" s="3">
         <v>46120</v>
@@ -48562,7 +48574,7 @@
         <v>0</v>
       </c>
       <c r="B846" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="C846" s="2">
         <v>40</v>
@@ -48612,7 +48624,7 @@
         <v>0</v>
       </c>
       <c r="B847" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C847" s="2">
         <v>30</v>
@@ -48621,10 +48633,10 @@
         <v>0</v>
       </c>
       <c r="E847" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="F847" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="G847" s="3">
         <v>46121</v>
@@ -48662,7 +48674,7 @@
         <v>0</v>
       </c>
       <c r="B848" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="C848" s="2">
         <v>1</v>
@@ -48671,10 +48683,10 @@
         <v>0</v>
       </c>
       <c r="E848" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="F848" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="G848" s="3">
         <v>46122</v>
@@ -48686,7 +48698,7 @@
         <v>46237</v>
       </c>
       <c r="J848" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K848" t="s">
         <v>54</v>
@@ -48712,7 +48724,7 @@
         <v>0</v>
       </c>
       <c r="B849" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="C849" s="2">
         <v>20</v>
@@ -48721,10 +48733,10 @@
         <v>0</v>
       </c>
       <c r="E849" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="F849" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="G849" s="3">
         <v>46125</v>
@@ -48762,7 +48774,7 @@
         <v>0</v>
       </c>
       <c r="B850" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="C850" s="2">
         <v>20</v>
@@ -48771,10 +48783,10 @@
         <v>0</v>
       </c>
       <c r="E850" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="F850" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="G850" s="3">
         <v>46125</v>
@@ -48812,7 +48824,7 @@
         <v>0</v>
       </c>
       <c r="B851" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="C851" s="2">
         <v>6</v>
@@ -48862,7 +48874,7 @@
         <v>0</v>
       </c>
       <c r="B852" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C852" s="2">
         <v>8</v>
@@ -48871,10 +48883,10 @@
         <v>0</v>
       </c>
       <c r="E852" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="F852" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="G852" s="3">
         <v>46125</v>
@@ -48886,7 +48898,7 @@
         <v>46223</v>
       </c>
       <c r="J852" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K852" t="s">
         <v>54</v>
@@ -48912,7 +48924,7 @@
         <v>0</v>
       </c>
       <c r="B853" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="C853" s="2">
         <v>8</v>
@@ -48921,10 +48933,10 @@
         <v>0</v>
       </c>
       <c r="E853" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="F853" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G853" s="3">
         <v>46125</v>
@@ -48936,7 +48948,7 @@
         <v>46216</v>
       </c>
       <c r="J853" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K853" t="s">
         <v>54</v>
@@ -48962,7 +48974,7 @@
         <v>0</v>
       </c>
       <c r="B854" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="C854" s="2">
         <v>1</v>
@@ -48971,10 +48983,10 @@
         <v>0</v>
       </c>
       <c r="E854" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="F854" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="G854" s="3">
         <v>46125</v>
@@ -49012,7 +49024,7 @@
         <v>0</v>
       </c>
       <c r="B855" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C855" s="2">
         <v>1</v>
@@ -49021,10 +49033,10 @@
         <v>0</v>
       </c>
       <c r="E855" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="F855" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="G855" s="3">
         <v>46125</v>
@@ -49062,7 +49074,7 @@
         <v>0</v>
       </c>
       <c r="B856" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="C856" s="2">
         <v>2</v>
@@ -49086,7 +49098,7 @@
         <v>46231</v>
       </c>
       <c r="J856" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K856" t="s">
         <v>54</v>
@@ -49112,7 +49124,7 @@
         <v>0</v>
       </c>
       <c r="B857" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C857" s="2">
         <v>60</v>
@@ -49162,7 +49174,7 @@
         <v>0</v>
       </c>
       <c r="B858" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C858" s="2">
         <v>20</v>
@@ -49212,7 +49224,7 @@
         <v>0</v>
       </c>
       <c r="B859" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C859" s="2">
         <v>2</v>
@@ -49230,10 +49242,10 @@
         <v>46127</v>
       </c>
       <c r="H859" s="3">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="I859" s="3">
-        <v>46188</v>
+        <v>46245</v>
       </c>
       <c r="J859" t="s">
         <v>554</v>
@@ -49262,7 +49274,7 @@
         <v>0</v>
       </c>
       <c r="B860" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="C860" s="2">
         <v>3</v>
@@ -49286,7 +49298,7 @@
         <v>46237</v>
       </c>
       <c r="J860" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K860" t="s">
         <v>54</v>
@@ -49312,7 +49324,7 @@
         <v>0</v>
       </c>
       <c r="B861" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C861" s="2">
         <v>2</v>
@@ -49336,7 +49348,7 @@
         <v>46202</v>
       </c>
       <c r="J861" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K861" t="s">
         <v>54</v>
@@ -49362,7 +49374,7 @@
         <v>0</v>
       </c>
       <c r="B862" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C862" s="2">
         <v>2</v>
@@ -49371,10 +49383,10 @@
         <v>0</v>
       </c>
       <c r="E862" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="F862" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G862" s="3">
         <v>46127</v>
@@ -49412,7 +49424,7 @@
         <v>0</v>
       </c>
       <c r="B863" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="C863" s="2">
         <v>2</v>
@@ -49421,10 +49433,10 @@
         <v>0</v>
       </c>
       <c r="E863" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="F863" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="G863" s="3">
         <v>46127</v>
@@ -49436,7 +49448,7 @@
         <v>46217</v>
       </c>
       <c r="J863" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K863" t="s">
         <v>54</v>
@@ -49462,7 +49474,7 @@
         <v>0</v>
       </c>
       <c r="B864" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="C864" s="2">
         <v>3</v>
@@ -49471,7 +49483,7 @@
         <v>0</v>
       </c>
       <c r="E864" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="F864" t="s">
         <v>1236</v>
@@ -49486,7 +49498,7 @@
         <v>46188</v>
       </c>
       <c r="J864" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K864" t="s">
         <v>54</v>
@@ -49512,7 +49524,7 @@
         <v>0</v>
       </c>
       <c r="B865" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="C865" s="2">
         <v>3</v>
@@ -49536,7 +49548,7 @@
         <v>46188</v>
       </c>
       <c r="J865" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K865" t="s">
         <v>54</v>
@@ -49562,7 +49574,7 @@
         <v>0</v>
       </c>
       <c r="B866" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="C866" s="2">
         <v>3</v>
@@ -49586,7 +49598,7 @@
         <v>46216</v>
       </c>
       <c r="J866" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K866" t="s">
         <v>54</v>
@@ -49612,7 +49624,7 @@
         <v>0</v>
       </c>
       <c r="B867" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C867" s="2">
         <v>3</v>
@@ -49636,7 +49648,7 @@
         <v>46216</v>
       </c>
       <c r="J867" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="K867" t="s">
         <v>54</v>
@@ -49662,7 +49674,7 @@
         <v>0</v>
       </c>
       <c r="B868" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="C868" s="2">
         <v>10</v>
@@ -49712,7 +49724,7 @@
         <v>0</v>
       </c>
       <c r="B869" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="C869" s="2">
         <v>10</v>
@@ -49762,7 +49774,7 @@
         <v>0</v>
       </c>
       <c r="B870" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C870" s="2">
         <v>1</v>
@@ -49771,10 +49783,10 @@
         <v>0</v>
       </c>
       <c r="E870" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="F870" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="G870" s="3">
         <v>46129</v>
@@ -49812,7 +49824,7 @@
         <v>0</v>
       </c>
       <c r="B871" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="C871" s="2">
         <v>3</v>
@@ -49821,10 +49833,10 @@
         <v>0</v>
       </c>
       <c r="E871" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="F871" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="G871" s="3">
         <v>46129</v>
@@ -49862,7 +49874,7 @@
         <v>0</v>
       </c>
       <c r="B872" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C872" s="2">
         <v>2</v>
@@ -49912,7 +49924,7 @@
         <v>0</v>
       </c>
       <c r="B873" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="C873" s="2">
         <v>2</v>
@@ -49936,7 +49948,7 @@
         <v>46188</v>
       </c>
       <c r="J873" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="K873" t="s">
         <v>54</v>
@@ -49962,7 +49974,7 @@
         <v>0</v>
       </c>
       <c r="B874" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C874" s="2">
         <v>1</v>
@@ -49971,10 +49983,10 @@
         <v>0</v>
       </c>
       <c r="E874" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="F874" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="G874" s="3">
         <v>46129</v>
@@ -50012,7 +50024,7 @@
         <v>0</v>
       </c>
       <c r="B875" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="C875" s="2">
         <v>1</v>
@@ -50021,10 +50033,10 @@
         <v>0</v>
       </c>
       <c r="E875" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="F875" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="G875" s="3">
         <v>46129</v>
@@ -50062,7 +50074,7 @@
         <v>0</v>
       </c>
       <c r="B876" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C876" s="2">
         <v>1</v>
@@ -50112,7 +50124,7 @@
         <v>0</v>
       </c>
       <c r="B877" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="C877" s="2">
         <v>1</v>
@@ -50162,7 +50174,7 @@
         <v>0</v>
       </c>
       <c r="B878" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="C878" s="2">
         <v>2</v>
@@ -50212,7 +50224,7 @@
         <v>0</v>
       </c>
       <c r="B879" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="C879" s="2">
         <v>6</v>
@@ -50262,7 +50274,7 @@
         <v>0</v>
       </c>
       <c r="B880" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="C880" s="2">
         <v>6</v>
@@ -50312,7 +50324,7 @@
         <v>0</v>
       </c>
       <c r="B881" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="C881" s="2">
         <v>1</v>
@@ -50321,10 +50333,10 @@
         <v>0</v>
       </c>
       <c r="E881" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="F881" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G881" s="3">
         <v>46132</v>
@@ -50362,7 +50374,7 @@
         <v>0</v>
       </c>
       <c r="B882" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="C882" s="2">
         <v>1</v>
@@ -50371,10 +50383,10 @@
         <v>0</v>
       </c>
       <c r="E882" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="F882" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G882" s="3">
         <v>46132</v>
@@ -50386,7 +50398,7 @@
         <v>46191</v>
       </c>
       <c r="J882" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="K882" t="s">
         <v>54</v>
@@ -50412,7 +50424,7 @@
         <v>0</v>
       </c>
       <c r="B883" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C883" s="2">
         <v>1</v>
@@ -50421,10 +50433,10 @@
         <v>0</v>
       </c>
       <c r="E883" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="F883" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G883" s="3">
         <v>46132</v>
@@ -50462,7 +50474,7 @@
         <v>0</v>
       </c>
       <c r="B884" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="C884" s="2">
         <v>1</v>
@@ -50471,10 +50483,10 @@
         <v>0</v>
       </c>
       <c r="E884" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="F884" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="G884" s="3">
         <v>46132</v>
@@ -50512,7 +50524,7 @@
         <v>0</v>
       </c>
       <c r="B885" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="C885" s="2">
         <v>4</v>
@@ -50562,7 +50574,7 @@
         <v>0</v>
       </c>
       <c r="B886" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C886" s="2">
         <v>4</v>
@@ -50612,7 +50624,7 @@
         <v>0</v>
       </c>
       <c r="B887" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="C887" s="2">
         <v>30</v>
@@ -50662,7 +50674,7 @@
         <v>0</v>
       </c>
       <c r="B888" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C888" s="2">
         <v>1</v>
@@ -50671,10 +50683,10 @@
         <v>0</v>
       </c>
       <c r="E888" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="F888" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="G888" s="3">
         <v>46133</v>
@@ -50712,7 +50724,7 @@
         <v>0</v>
       </c>
       <c r="B889" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="C889" s="2">
         <v>2</v>
@@ -50762,7 +50774,7 @@
         <v>0</v>
       </c>
       <c r="B890" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="C890" s="2">
         <v>2</v>
@@ -50812,7 +50824,7 @@
         <v>0</v>
       </c>
       <c r="B891" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="C891" s="2">
         <v>2</v>
@@ -50862,7 +50874,7 @@
         <v>0</v>
       </c>
       <c r="B892" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="C892" s="2">
         <v>2</v>
@@ -50912,7 +50924,7 @@
         <v>0</v>
       </c>
       <c r="B893" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="C893" s="2">
         <v>40</v>
@@ -50962,7 +50974,7 @@
         <v>0</v>
       </c>
       <c r="B894" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="C894" s="2">
         <v>40</v>
@@ -51012,7 +51024,7 @@
         <v>0</v>
       </c>
       <c r="B895" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="C895" s="2">
         <v>30</v>
@@ -51062,7 +51074,7 @@
         <v>0</v>
       </c>
       <c r="B896" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="C896" s="2">
         <v>10</v>
@@ -51071,10 +51083,10 @@
         <v>0</v>
       </c>
       <c r="E896" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="F896" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="G896" s="3">
         <v>46135</v>
@@ -51112,7 +51124,7 @@
         <v>0</v>
       </c>
       <c r="B897" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="C897" s="2">
         <v>5</v>
@@ -51121,10 +51133,10 @@
         <v>0</v>
       </c>
       <c r="E897" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="F897" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="G897" s="3">
         <v>46135</v>
@@ -51162,7 +51174,7 @@
         <v>0</v>
       </c>
       <c r="B898" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C898" s="2">
         <v>1</v>
@@ -51212,7 +51224,7 @@
         <v>0</v>
       </c>
       <c r="B899" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C899" s="2">
         <v>6</v>
@@ -51262,7 +51274,7 @@
         <v>0</v>
       </c>
       <c r="B900" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C900" s="2">
         <v>3</v>
@@ -51271,7 +51283,7 @@
         <v>0</v>
       </c>
       <c r="E900" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F900" t="s">
         <v>799</v>
@@ -51312,7 +51324,7 @@
         <v>0</v>
       </c>
       <c r="B901" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C901" s="2">
         <v>2</v>
@@ -51321,10 +51333,10 @@
         <v>0</v>
       </c>
       <c r="E901" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="F901" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G901" s="3">
         <v>46136</v>
@@ -51362,7 +51374,7 @@
         <v>0</v>
       </c>
       <c r="B902" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="C902" s="2">
         <v>2</v>
@@ -51371,10 +51383,10 @@
         <v>0</v>
       </c>
       <c r="E902" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="F902" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G902" s="3">
         <v>46136</v>
@@ -51412,7 +51424,7 @@
         <v>0</v>
       </c>
       <c r="B903" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C903" s="2">
         <v>2</v>
@@ -51462,7 +51474,7 @@
         <v>0</v>
       </c>
       <c r="B904" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="C904" s="2">
         <v>2</v>
@@ -51486,7 +51498,7 @@
         <v>46223</v>
       </c>
       <c r="J904" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K904" t="s">
         <v>54</v>
@@ -51512,7 +51524,7 @@
         <v>0</v>
       </c>
       <c r="B905" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="C905" s="2">
         <v>3</v>
@@ -51562,7 +51574,7 @@
         <v>0</v>
       </c>
       <c r="B906" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="C906" s="2">
         <v>3</v>
@@ -51571,7 +51583,7 @@
         <v>0</v>
       </c>
       <c r="E906" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="F906" t="s">
         <v>1236</v>
@@ -51612,7 +51624,7 @@
         <v>0</v>
       </c>
       <c r="B907" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="C907" s="2">
         <v>6</v>
@@ -51636,7 +51648,7 @@
         <v>46223</v>
       </c>
       <c r="J907" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K907" t="s">
         <v>54</v>
@@ -51662,7 +51674,7 @@
         <v>0</v>
       </c>
       <c r="B908" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="C908" s="2">
         <v>6</v>
@@ -51686,7 +51698,7 @@
         <v>46223</v>
       </c>
       <c r="J908" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K908" t="s">
         <v>54</v>
@@ -51712,7 +51724,7 @@
         <v>0</v>
       </c>
       <c r="B909" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="C909" s="2">
         <v>4</v>
@@ -51736,7 +51748,7 @@
         <v>46231</v>
       </c>
       <c r="J909" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K909" t="s">
         <v>54</v>
@@ -51762,7 +51774,7 @@
         <v>0</v>
       </c>
       <c r="B910" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="C910" s="2">
         <v>4</v>
@@ -51786,7 +51798,7 @@
         <v>46202</v>
       </c>
       <c r="J910" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K910" t="s">
         <v>54</v>
@@ -51812,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="B911" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C911" s="2">
         <v>4</v>
@@ -51862,7 +51874,7 @@
         <v>0</v>
       </c>
       <c r="B912" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C912" s="2">
         <v>4</v>
@@ -51886,7 +51898,7 @@
         <v>46223</v>
       </c>
       <c r="J912" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K912" t="s">
         <v>54</v>
@@ -51912,7 +51924,7 @@
         <v>0</v>
       </c>
       <c r="B913" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C913" s="2">
         <v>6</v>
@@ -51936,7 +51948,7 @@
         <v>46204</v>
       </c>
       <c r="J913" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K913" t="s">
         <v>54</v>
@@ -51962,7 +51974,7 @@
         <v>0</v>
       </c>
       <c r="B914" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="C914" s="2">
         <v>2</v>
@@ -52012,7 +52024,7 @@
         <v>0</v>
       </c>
       <c r="B915" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C915" s="2">
         <v>4</v>
@@ -52021,7 +52033,7 @@
         <v>0</v>
       </c>
       <c r="E915" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="F915" t="s">
         <v>799</v>
@@ -52062,7 +52074,7 @@
         <v>0</v>
       </c>
       <c r="B916" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C916" s="2">
         <v>4</v>
@@ -52112,7 +52124,7 @@
         <v>0</v>
       </c>
       <c r="B917" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C917" s="2">
         <v>4</v>
@@ -52162,7 +52174,7 @@
         <v>0</v>
       </c>
       <c r="B918" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C918" s="2">
         <v>4</v>
@@ -52186,7 +52198,7 @@
         <v>46224</v>
       </c>
       <c r="J918" t="s">
-        <v>554</v>
+        <v>1992</v>
       </c>
       <c r="K918" t="s">
         <v>54</v>
@@ -52212,7 +52224,7 @@
         <v>0</v>
       </c>
       <c r="B919" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="C919" s="2">
         <v>4</v>
@@ -52262,7 +52274,7 @@
         <v>0</v>
       </c>
       <c r="B920" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="C920" s="2">
         <v>1</v>
@@ -52271,10 +52283,10 @@
         <v>0</v>
       </c>
       <c r="E920" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="F920" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="G920" s="3">
         <v>46141</v>
@@ -52286,7 +52298,7 @@
         <v>46210</v>
       </c>
       <c r="J920" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="K920" t="s">
         <v>54</v>
@@ -52312,7 +52324,7 @@
         <v>0</v>
       </c>
       <c r="B921" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C921" s="2">
         <v>20</v>
@@ -52362,7 +52374,7 @@
         <v>0</v>
       </c>
       <c r="B922" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C922" s="2">
         <v>3</v>
@@ -52371,7 +52383,7 @@
         <v>0</v>
       </c>
       <c r="E922" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="F922" t="s">
         <v>1277</v>
@@ -52412,7 +52424,7 @@
         <v>0</v>
       </c>
       <c r="B923" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C923" s="2">
         <v>6</v>
@@ -52462,7 +52474,7 @@
         <v>0</v>
       </c>
       <c r="B924" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C924" s="2">
         <v>1000</v>
@@ -52512,7 +52524,7 @@
         <v>0</v>
       </c>
       <c r="B925" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C925" s="2">
         <v>1</v>
@@ -52521,10 +52533,10 @@
         <v>0</v>
       </c>
       <c r="E925" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F925" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="G925" s="3">
         <v>46147</v>
@@ -52536,7 +52548,7 @@
         <v>46210</v>
       </c>
       <c r="J925" t="s">
-        <v>21</v>
+        <v>1956</v>
       </c>
       <c r="K925" t="s">
         <v>54</v>
@@ -52559,46 +52571,46 @@
     </row>
     <row r="926" spans="1:16">
       <c r="A926" t="s">
-        <v>2017</v>
+        <v>0</v>
       </c>
       <c r="B926" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C926" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D926" s="2">
         <v>0</v>
       </c>
       <c r="E926" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="F926" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="G926" s="3">
-        <v>46043</v>
+        <v>46148</v>
       </c>
       <c r="H926" s="3">
-        <v>46051</v>
+        <v>46148</v>
       </c>
       <c r="I926" s="3">
-        <v>46057</v>
+        <v>46245</v>
       </c>
       <c r="J926" t="s">
-        <v>2021</v>
+        <v>554</v>
       </c>
       <c r="K926" t="s">
-        <v>2022</v>
+        <v>54</v>
       </c>
       <c r="L926" s="3">
-        <v>46043</v>
+        <v>46148</v>
       </c>
       <c r="M926" t="s">
         <v>6</v>
       </c>
       <c r="N926" t="s">
-        <v>2023</v>
+        <v>32</v>
       </c>
       <c r="O926" t="s">
         <v>8</v>
@@ -52609,46 +52621,46 @@
     </row>
     <row r="927" spans="1:16">
       <c r="A927" t="s">
-        <v>2017</v>
+        <v>0</v>
       </c>
       <c r="B927" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C927" s="2">
+        <v>2</v>
+      </c>
+      <c r="D927" s="2">
+        <v>0</v>
+      </c>
+      <c r="E927" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F927" t="s">
         <v>2024</v>
       </c>
-      <c r="C927" s="2">
-        <v>1</v>
-      </c>
-      <c r="D927" s="2">
-        <v>0</v>
-      </c>
-      <c r="E927" t="s">
-        <v>2025</v>
-      </c>
-      <c r="F927" t="s">
-        <v>2026</v>
-      </c>
       <c r="G927" s="3">
-        <v>46057</v>
+        <v>46149</v>
       </c>
       <c r="H927" s="3">
-        <v>46076</v>
+        <v>46149</v>
       </c>
       <c r="I927" s="3">
-        <v>46083</v>
+        <v>46234</v>
       </c>
       <c r="J927" t="s">
-        <v>2027</v>
+        <v>21</v>
       </c>
       <c r="K927" t="s">
-        <v>2022</v>
+        <v>5</v>
       </c>
       <c r="L927" s="3">
-        <v>46057</v>
+        <v>46149</v>
       </c>
       <c r="M927" t="s">
         <v>6</v>
       </c>
       <c r="N927" t="s">
-        <v>2023</v>
+        <v>32</v>
       </c>
       <c r="O927" t="s">
         <v>8</v>
@@ -52659,10 +52671,10 @@
     </row>
     <row r="928" spans="1:16">
       <c r="A928" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B928" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C928" s="2">
         <v>1</v>
@@ -52671,34 +52683,34 @@
         <v>0</v>
       </c>
       <c r="E928" t="s">
+        <v>2027</v>
+      </c>
+      <c r="F928" t="s">
+        <v>2028</v>
+      </c>
+      <c r="G928" s="3">
+        <v>46043</v>
+      </c>
+      <c r="H928" s="3">
+        <v>46051</v>
+      </c>
+      <c r="I928" s="3">
+        <v>46057</v>
+      </c>
+      <c r="J928" t="s">
         <v>2029</v>
       </c>
-      <c r="F928" t="s">
+      <c r="K928" t="s">
         <v>2030</v>
       </c>
-      <c r="G928" s="3">
-        <v>46114</v>
-      </c>
-      <c r="H928" s="3">
-        <v>46148</v>
-      </c>
-      <c r="I928" s="3">
-        <v>46148</v>
-      </c>
-      <c r="J928" t="s">
+      <c r="L928" s="3">
+        <v>46043</v>
+      </c>
+      <c r="M928" t="s">
+        <v>6</v>
+      </c>
+      <c r="N928" t="s">
         <v>2031</v>
-      </c>
-      <c r="K928" t="s">
-        <v>2022</v>
-      </c>
-      <c r="L928" s="3">
-        <v>46114</v>
-      </c>
-      <c r="M928" t="s">
-        <v>6</v>
-      </c>
-      <c r="N928" t="s">
-        <v>2023</v>
       </c>
       <c r="O928" t="s">
         <v>8</v>
@@ -52709,7 +52721,7 @@
     </row>
     <row r="929" spans="1:16">
       <c r="A929" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B929" t="s">
         <v>2032</v>
@@ -52718,7 +52730,7 @@
         <v>1</v>
       </c>
       <c r="D929" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E929" t="s">
         <v>2033</v>
@@ -52727,28 +52739,28 @@
         <v>2034</v>
       </c>
       <c r="G929" s="3">
-        <v>46122</v>
+        <v>46057</v>
       </c>
       <c r="H929" s="3">
-        <v>46142</v>
+        <v>46076</v>
       </c>
       <c r="I929" s="3">
-        <v>46148</v>
+        <v>46083</v>
       </c>
       <c r="J929" t="s">
         <v>2035</v>
       </c>
       <c r="K929" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="L929" s="3">
-        <v>46122</v>
+        <v>46057</v>
       </c>
       <c r="M929" t="s">
         <v>6</v>
       </c>
       <c r="N929" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="O929" t="s">
         <v>8</v>
@@ -52759,7 +52771,7 @@
     </row>
     <row r="930" spans="1:16">
       <c r="A930" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B930" t="s">
         <v>2036</v>
@@ -52777,28 +52789,28 @@
         <v>2038</v>
       </c>
       <c r="G930" s="3">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="H930" s="3">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="I930" s="3">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="J930" t="s">
         <v>2039</v>
       </c>
       <c r="K930" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="L930" s="3">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="M930" t="s">
         <v>6</v>
       </c>
       <c r="N930" t="s">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="O930" t="s">
         <v>8</v>
@@ -52809,7 +52821,7 @@
     </row>
     <row r="931" spans="1:16">
       <c r="A931" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B931" t="s">
         <v>2040</v>
@@ -52827,33 +52839,83 @@
         <v>2042</v>
       </c>
       <c r="G931" s="3">
-        <v>46140</v>
+        <v>46135</v>
       </c>
       <c r="H931" s="3">
-        <v>46140</v>
+        <v>46135</v>
       </c>
       <c r="I931" s="3">
         <v>46147</v>
       </c>
       <c r="J931" t="s">
+        <v>2043</v>
+      </c>
+      <c r="K931" t="s">
+        <v>2030</v>
+      </c>
+      <c r="L931" s="3">
+        <v>46135</v>
+      </c>
+      <c r="M931" t="s">
+        <v>6</v>
+      </c>
+      <c r="N931" t="s">
         <v>2031</v>
       </c>
-      <c r="K931" t="s">
-        <v>2022</v>
-      </c>
-      <c r="L931" s="3">
+      <c r="O931" t="s">
+        <v>8</v>
+      </c>
+      <c r="P931" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="932" spans="1:16">
+      <c r="A932" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B932" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C932" s="2">
+        <v>1</v>
+      </c>
+      <c r="D932" s="2">
+        <v>0</v>
+      </c>
+      <c r="E932" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F932" t="s">
+        <v>2046</v>
+      </c>
+      <c r="G932" s="3">
         <v>46140</v>
       </c>
-      <c r="M931" t="s">
-        <v>6</v>
-      </c>
-      <c r="N931" t="s">
-        <v>2023</v>
-      </c>
-      <c r="O931" t="s">
-        <v>8</v>
-      </c>
-      <c r="P931" t="s">
+      <c r="H932" s="3">
+        <v>46140</v>
+      </c>
+      <c r="I932" s="3">
+        <v>46147</v>
+      </c>
+      <c r="J932" t="s">
+        <v>2039</v>
+      </c>
+      <c r="K932" t="s">
+        <v>2030</v>
+      </c>
+      <c r="L932" s="3">
+        <v>46140</v>
+      </c>
+      <c r="M932" t="s">
+        <v>6</v>
+      </c>
+      <c r="N932" t="s">
+        <v>2031</v>
+      </c>
+      <c r="O932" t="s">
+        <v>8</v>
+      </c>
+      <c r="P932" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Newdata/鑄件未交.XLSX
+++ b/Newdata/鑄件未交.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9306" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9316" uniqueCount="2044">
   <si>
     <t>ZP04</t>
   </si>
@@ -6052,6 +6052,9 @@
   </si>
   <si>
     <t>400006574</t>
+  </si>
+  <si>
+    <t>400006575</t>
   </si>
   <si>
     <t>ZP09</t>
@@ -6246,7 +6249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P930"/>
+  <dimension ref="A1:P931"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="6" customWidth="1"/>
@@ -6269,52 +6272,52 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -52611,46 +52614,46 @@
     </row>
     <row r="928" spans="1:16">
       <c r="A928" t="s">
+        <v>0</v>
+      </c>
+      <c r="B928" t="s">
         <v>2013</v>
       </c>
-      <c r="B928" t="s">
-        <v>2014</v>
-      </c>
       <c r="C928" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D928" s="2">
         <v>0</v>
       </c>
       <c r="E928" t="s">
-        <v>2015</v>
+        <v>1970</v>
       </c>
       <c r="F928" t="s">
-        <v>2016</v>
+        <v>1263</v>
       </c>
       <c r="G928" s="3">
-        <v>46043</v>
+        <v>46156</v>
       </c>
       <c r="H928" s="3">
-        <v>46051</v>
+        <v>46158</v>
       </c>
       <c r="I928" s="3">
-        <v>46057</v>
+        <v>46213</v>
       </c>
       <c r="J928" t="s">
-        <v>2017</v>
+        <v>21</v>
       </c>
       <c r="K928" t="s">
-        <v>2018</v>
+        <v>5</v>
       </c>
       <c r="L928" s="3">
-        <v>46043</v>
+        <v>46156</v>
       </c>
       <c r="M928" t="s">
         <v>6</v>
       </c>
       <c r="N928" t="s">
-        <v>2019</v>
+        <v>32</v>
       </c>
       <c r="O928" t="s">
         <v>8</v>
@@ -52661,10 +52664,10 @@
     </row>
     <row r="929" spans="1:16">
       <c r="A929" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B929" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C929" s="2">
         <v>1</v>
@@ -52673,34 +52676,34 @@
         <v>0</v>
       </c>
       <c r="E929" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="F929" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="G929" s="3">
-        <v>46114</v>
+        <v>46043</v>
       </c>
       <c r="H929" s="3">
-        <v>46148</v>
+        <v>46051</v>
       </c>
       <c r="I929" s="3">
-        <v>46148</v>
+        <v>46057</v>
       </c>
       <c r="J929" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="K929" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="L929" s="3">
-        <v>46114</v>
+        <v>46043</v>
       </c>
       <c r="M929" t="s">
         <v>6</v>
       </c>
       <c r="N929" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="O929" t="s">
         <v>8</v>
@@ -52711,10 +52714,10 @@
     </row>
     <row r="930" spans="1:16">
       <c r="A930" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B930" t="s">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C930" s="2">
         <v>1</v>
@@ -52723,39 +52726,89 @@
         <v>0</v>
       </c>
       <c r="E930" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F930" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G930" s="3">
+        <v>46114</v>
+      </c>
+      <c r="H930" s="3">
+        <v>46148</v>
+      </c>
+      <c r="I930" s="3">
+        <v>46148</v>
+      </c>
+      <c r="J930" t="s">
+        <v>2024</v>
+      </c>
+      <c r="K930" t="s">
+        <v>2019</v>
+      </c>
+      <c r="L930" s="3">
+        <v>46114</v>
+      </c>
+      <c r="M930" t="s">
+        <v>6</v>
+      </c>
+      <c r="N930" t="s">
+        <v>2020</v>
+      </c>
+      <c r="O930" t="s">
+        <v>8</v>
+      </c>
+      <c r="P930" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="931" spans="1:16">
+      <c r="A931" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B931" t="s">
         <v>2025</v>
       </c>
-      <c r="F930" t="s">
+      <c r="C931" s="2">
+        <v>1</v>
+      </c>
+      <c r="D931" s="2">
+        <v>0</v>
+      </c>
+      <c r="E931" t="s">
         <v>2026</v>
       </c>
-      <c r="G930" s="3">
+      <c r="F931" t="s">
+        <v>2027</v>
+      </c>
+      <c r="G931" s="3">
         <v>46140</v>
       </c>
-      <c r="H930" s="3">
+      <c r="H931" s="3">
         <v>46140</v>
       </c>
-      <c r="I930" s="3">
+      <c r="I931" s="3">
         <v>46147</v>
       </c>
-      <c r="J930" t="s">
-        <v>2023</v>
-      </c>
-      <c r="K930" t="s">
-        <v>2018</v>
-      </c>
-      <c r="L930" s="3">
+      <c r="J931" t="s">
+        <v>2024</v>
+      </c>
+      <c r="K931" t="s">
+        <v>2019</v>
+      </c>
+      <c r="L931" s="3">
         <v>46140</v>
       </c>
-      <c r="M930" t="s">
-        <v>6</v>
-      </c>
-      <c r="N930" t="s">
-        <v>2019</v>
-      </c>
-      <c r="O930" t="s">
-        <v>8</v>
-      </c>
-      <c r="P930" t="s">
+      <c r="M931" t="s">
+        <v>6</v>
+      </c>
+      <c r="N931" t="s">
+        <v>2020</v>
+      </c>
+      <c r="O931" t="s">
+        <v>8</v>
+      </c>
+      <c r="P931" t="s">
         <v>9</v>
       </c>
     </row>
